--- a/ZonasEscolares/excels/LIMA-LIMA-SANTA_ANITA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-SANTA_ANITA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SANTA_ANITA</t>
+          <t>SANTA ANITA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-SANTA_ANITA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-SANTA_ANITA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>053 SANTA ROSITA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.04821</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-76.97774</v>
-      </c>
-      <c r="I2" t="n">
-        <v>379</v>
-      </c>
-      <c r="J2" t="n">
-        <v>15</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.04821</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-76.97774</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>056 VIRGEN DE FATIMA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.04921</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-76.96923</v>
-      </c>
-      <c r="I3" t="n">
-        <v>234</v>
-      </c>
-      <c r="J3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.04921</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-76.96923</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>064</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.041</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-76.9682</v>
-      </c>
-      <c r="I4" t="n">
-        <v>359</v>
-      </c>
-      <c r="J4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.041</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-76.9682</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>0096</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.04078</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-76.9866</v>
-      </c>
-      <c r="I5" t="n">
-        <v>345</v>
-      </c>
-      <c r="J5" t="n">
-        <v>18</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.04078</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-76.9866</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>0097 PATRICIA ANTONIA LOPEZ</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.050626</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-76.980906</v>
-      </c>
-      <c r="I6" t="n">
-        <v>716</v>
-      </c>
-      <c r="J6" t="n">
-        <v>35</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.050626</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-76.980906</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>0101 SHUJI KITAMURA</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.04268</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-76.97738</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2447</v>
-      </c>
-      <c r="J7" t="n">
-        <v>92</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.04268</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-76.97738</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2447</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>0106 ABRAHAM VALDELOMAR / 106 ABRAHAM VALDELOMAR</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.04765</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-76.97062</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1600</v>
-      </c>
-      <c r="J8" t="n">
-        <v>70</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.04765</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-76.97062</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>0108 SANTA ROSA DE QUIVES</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.05326</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-76.97946</v>
-      </c>
-      <c r="I9" t="n">
-        <v>925</v>
-      </c>
-      <c r="J9" t="n">
-        <v>38</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.05326</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-76.97946</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>111</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.04826</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-76.96862</v>
-      </c>
-      <c r="I10" t="n">
-        <v>247</v>
-      </c>
-      <c r="J10" t="n">
-        <v>11</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.04826</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-76.96862</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>123 LOS ARBOLES</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.045935</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-76.98478299999999</v>
-      </c>
-      <c r="I11" t="n">
-        <v>742</v>
-      </c>
-      <c r="J11" t="n">
-        <v>31</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.045935</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-76.984783</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>742</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>0124 GLORIOSA LEGION CACERES</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.05231</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-76.98433</v>
-      </c>
-      <c r="I12" t="n">
-        <v>686</v>
-      </c>
-      <c r="J12" t="n">
-        <v>29</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.05231</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-76.98433</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>129 YAMAGUCHI</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.0485</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-76.97721</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1168</v>
-      </c>
-      <c r="J13" t="n">
-        <v>58</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.0485</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-76.97721</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1168</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>152</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.03922</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-76.95862</v>
-      </c>
-      <c r="I14" t="n">
-        <v>266</v>
-      </c>
-      <c r="J14" t="n">
-        <v>11</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.03922</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-76.95862</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>186</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.03233</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-76.95113000000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>322</v>
-      </c>
-      <c r="J15" t="n">
-        <v>15</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.03233</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-76.95113</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>1137 JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.05015</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-76.96337</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2186</v>
-      </c>
-      <c r="J16" t="n">
-        <v>104</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.05015</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-76.96337</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2186</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>1211 JOSE MARIA ARGUEDAS ALTAMIRANO</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.04679</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-76.95845</v>
-      </c>
-      <c r="I17" t="n">
-        <v>810</v>
-      </c>
-      <c r="J17" t="n">
-        <v>47</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.04679</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-76.95845</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>1219 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.04534</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-76.95422000000001</v>
-      </c>
-      <c r="I18" t="n">
-        <v>837</v>
-      </c>
-      <c r="J18" t="n">
-        <v>35</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.04534</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-76.95422</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>1221 MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.0397</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-76.96022000000001</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1261</v>
-      </c>
-      <c r="J19" t="n">
-        <v>60</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.0397</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-76.96022</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1261</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>1253 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.03969</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-76.96191</v>
-      </c>
-      <c r="I20" t="n">
-        <v>487</v>
-      </c>
-      <c r="J20" t="n">
-        <v>19</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.03969</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-76.96191</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>1256 ALFONSO UGARTE</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.03028</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-76.95218</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1194</v>
-      </c>
-      <c r="J21" t="n">
-        <v>44</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.03028</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-76.95218</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1194</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>1273 MI PERU</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.0312</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-76.94655</v>
-      </c>
-      <c r="I22" t="n">
-        <v>574</v>
-      </c>
-      <c r="J22" t="n">
-        <v>23</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.0312</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-76.94655</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>JUAN VALER SANDOVAL</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-12.03117</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-76.95910000000001</v>
-      </c>
-      <c r="I23" t="n">
-        <v>455</v>
-      </c>
-      <c r="J23" t="n">
-        <v>19</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12.03117</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-76.9591</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>RODOLFO HORACIO ZEBALLOS GAMES</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-12.03202</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-76.96276</v>
-      </c>
-      <c r="I24" t="n">
-        <v>667</v>
-      </c>
-      <c r="J24" t="n">
-        <v>29</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.03202</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-76.96276</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>ALFONSO UGARTE</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-12.04823</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-76.97547</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1443</v>
-      </c>
-      <c r="J25" t="n">
-        <v>59</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-12.04823</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-76.97547</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1443</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-12.0438</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-76.97591</v>
-      </c>
-      <c r="I26" t="n">
-        <v>230</v>
-      </c>
-      <c r="J26" t="n">
-        <v>14</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-12.0438</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-76.97591</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>FRAY PEDRO URRACA</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-12.04273</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-76.9854</v>
-      </c>
-      <c r="I27" t="n">
-        <v>42</v>
-      </c>
-      <c r="J27" t="n">
-        <v>12</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-12.04273</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-76.9854</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>MONITOR HUASCAR</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-12.04313</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-76.97796</v>
-      </c>
-      <c r="I28" t="n">
-        <v>625</v>
-      </c>
-      <c r="J28" t="n">
-        <v>24</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-12.04313</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-76.97796</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-12.04432</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-76.97060999999999</v>
-      </c>
-      <c r="I29" t="n">
-        <v>324</v>
-      </c>
-      <c r="J29" t="n">
-        <v>16</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-12.04432</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-76.97061</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>SAN AGUSTIN</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-12.03146</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-76.96053000000001</v>
-      </c>
-      <c r="I30" t="n">
-        <v>610</v>
-      </c>
-      <c r="J30" t="n">
-        <v>18</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-12.03146</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-76.96053</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>VIRGEN DE FATIMA MILAGROSA</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-12.03809</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-76.96272</v>
-      </c>
-      <c r="I31" t="n">
-        <v>253</v>
-      </c>
-      <c r="J31" t="n">
-        <v>18</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-12.03809</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-76.96272</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>INGENIEROS &amp; ARQUITECTOS UNI</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-12.04967</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-76.97754</v>
-      </c>
-      <c r="I32" t="n">
-        <v>257</v>
-      </c>
-      <c r="J32" t="n">
-        <v>15</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-12.04967</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-76.97754</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>WILLIAM SHAKESPEARE</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-12.02888</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-76.94631</v>
-      </c>
-      <c r="I33" t="n">
-        <v>330</v>
-      </c>
-      <c r="J33" t="n">
-        <v>24</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-12.02888</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-76.94631</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>JUAN ESPINOZA MEDRANO</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-12.03199</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-76.95977000000001</v>
-      </c>
-      <c r="I34" t="n">
-        <v>738</v>
-      </c>
-      <c r="J34" t="n">
-        <v>33</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-12.03199</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-76.95977</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>RICARDO PALMA</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-12.04073</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-76.96935000000001</v>
-      </c>
-      <c r="I35" t="n">
-        <v>506</v>
-      </c>
-      <c r="J35" t="n">
-        <v>28</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-12.04073</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-76.96935</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>TRILCE DE SANTA ANITA</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-12.03276</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-76.95225000000001</v>
-      </c>
-      <c r="I36" t="n">
-        <v>614</v>
-      </c>
-      <c r="J36" t="n">
-        <v>39</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-12.03276</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-76.95225</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>CESAR VALLEJO DE LAS PRADERAS</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-12.0329</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-76.96281</v>
-      </c>
-      <c r="I37" t="n">
-        <v>352</v>
-      </c>
-      <c r="J37" t="n">
-        <v>18</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-12.0329</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-76.96281</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>TECHNOLOGY SCHOOLS DE SANTA ANITA</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-12.04639</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-76.95759</v>
-      </c>
-      <c r="I38" t="n">
-        <v>769</v>
-      </c>
-      <c r="J38" t="n">
-        <v>41</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-12.04639</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-76.95759</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>DORADO SCHOOL</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-12.03148</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-76.94955</v>
-      </c>
-      <c r="I39" t="n">
-        <v>232</v>
-      </c>
-      <c r="J39" t="n">
-        <v>24</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-12.03148</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-76.94955</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>153 FORTALEZA</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-12.02847</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-76.94513999999999</v>
-      </c>
-      <c r="I40" t="n">
-        <v>321</v>
-      </c>
-      <c r="J40" t="n">
-        <v>16</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-12.02847</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-76.94514</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>TECHNOLOGY SCHOOLS LUCUMOS</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-12.0302</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-76.95442</v>
-      </c>
-      <c r="I41" t="n">
-        <v>760</v>
-      </c>
-      <c r="J41" t="n">
-        <v>13</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-12.0302</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-76.95442</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>CIBERT SANTA ANITA</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-12.04325</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-76.97251</v>
-      </c>
-      <c r="I42" t="n">
-        <v>205</v>
-      </c>
-      <c r="J42" t="n">
-        <v>25</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-12.04325</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-76.97251</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>BOURBAKI</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-12.04457</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-76.97474</v>
-      </c>
-      <c r="I43" t="n">
-        <v>42</v>
-      </c>
-      <c r="J43" t="n">
-        <v>12</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-12.04457</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-76.97474</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>LA VILLA DE SANTO MARTIN</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-12.04245</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-76.96174000000001</v>
-      </c>
-      <c r="I44" t="n">
-        <v>238</v>
-      </c>
-      <c r="J44" t="n">
-        <v>11</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-12.04245</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-76.96174</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>LOS EDUCADORES</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-12.03531</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-76.96534</v>
-      </c>
-      <c r="I45" t="n">
-        <v>261</v>
-      </c>
-      <c r="J45" t="n">
-        <v>8</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-12.03531</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-76.96534</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>TECHNOLOGY SCHOOLS DE LOS FICUS I</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-12.0465</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-76.97565</v>
-      </c>
-      <c r="I46" t="n">
-        <v>850</v>
-      </c>
-      <c r="J46" t="n">
-        <v>39</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-12.0465</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-76.97565</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>MIS PRIMEROS PASOS</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-12.03554</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-76.96428</v>
-      </c>
-      <c r="I47" t="n">
-        <v>220</v>
-      </c>
-      <c r="J47" t="n">
-        <v>10</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-12.03554</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-76.96428</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>MAHANAIM</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-12.03702</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-76.96868000000001</v>
-      </c>
-      <c r="I48" t="n">
-        <v>363</v>
-      </c>
-      <c r="J48" t="n">
-        <v>16</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-12.03702</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-76.96868</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>SACO OLIVEROS HELICOIDAL</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-12.0418</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-76.95632000000001</v>
-      </c>
-      <c r="I49" t="n">
-        <v>1571</v>
-      </c>
-      <c r="J49" t="n">
-        <v>44</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-12.0418</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-76.95632</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1571</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-12.04873</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-76.97141000000001</v>
-      </c>
-      <c r="I50" t="n">
-        <v>782</v>
-      </c>
-      <c r="J50" t="n">
-        <v>42</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-12.04873</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-76.97141</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>782</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>RED SCHOOL</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-12.05405</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-76.97714999999999</v>
-      </c>
-      <c r="I51" t="n">
-        <v>213</v>
-      </c>
-      <c r="J51" t="n">
-        <v>5</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-12.05405</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-76.97715</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-LIMA-SANTA_ANITA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-SANTA_ANITA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>338624</t>
+          <t>338643</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>053 SANTA ROSITA</t>
+          <t>056 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.04821</t>
+          <t>-12.04921</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.97774</t>
+          <t>-76.96923</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>234</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,27 +563,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>338643</t>
+          <t>777289</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>056 VIRGEN DE FATIMA</t>
+          <t>MIS PRIMEROS PASOS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.04921</t>
+          <t>-12.03554</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.96923</t>
+          <t>-76.96428</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>338657</t>
+          <t>338817</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>064</t>
+          <t>1137 JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.041</t>
+          <t>-12.05015</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.9682</t>
+          <t>-76.96337</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>104</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>338676</t>
+          <t>338737</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>111</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.04078</t>
+          <t>-12.04826</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.9866</t>
+          <t>-76.96862</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>247</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>338681</t>
+          <t>338780</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0097 PATRICIA ANTONIA LOPEZ</t>
+          <t>152</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.050626</t>
+          <t>-12.03922</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.980906</t>
+          <t>-76.95862</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>266</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>338695</t>
+          <t>721122</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0101 SHUJI KITAMURA</t>
+          <t>LA VILLA DE SANTO MARTIN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.04268</t>
+          <t>-12.04245</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.97738</t>
+          <t>-76.96174</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2447</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>338704</t>
+          <t>339416</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0106 ABRAHAM VALDELOMAR / 106 ABRAHAM VALDELOMAR</t>
+          <t>FRAY PEDRO URRACA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.04765</t>
+          <t>-12.04273</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.97062</t>
+          <t>-76.9854</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>338723</t>
+          <t>720684</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0108 SANTA ROSA DE QUIVES</t>
+          <t>BOURBAKI</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.05326</t>
+          <t>-12.04457</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.97946</t>
+          <t>-76.97474</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>338737</t>
+          <t>619450</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>TECHNOLOGY SCHOOLS LUCUMOS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.04826</t>
+          <t>-12.0302</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.96862</t>
+          <t>-76.95442</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>760</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>338742</t>
+          <t>339317</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>123 LOS ARBOLES</t>
+          <t>CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.045935</t>
+          <t>-12.0438</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.984783</t>
+          <t>-76.97591</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>230</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>338756</t>
+          <t>338624</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0124 GLORIOSA LEGION CACERES</t>
+          <t>053 SANTA ROSITA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.05231</t>
+          <t>-12.04821</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.98433</t>
+          <t>-76.97774</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>379</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>338761</t>
+          <t>338657</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>129 YAMAGUCHI</t>
+          <t>064</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.0485</t>
+          <t>-12.041</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.97721</t>
+          <t>-76.9682</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>359</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>338780</t>
+          <t>338799</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>186</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.03922</t>
+          <t>-12.03233</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.95862</t>
+          <t>-76.95113</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>322</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,27 +1307,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>338799</t>
+          <t>339831</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>INGENIEROS &amp; ARQUITECTOS UNI</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.03233</t>
+          <t>-12.04967</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.95113</t>
+          <t>-76.97754</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>257</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>338817</t>
+          <t>339652</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1137 JOSE ANTONIO ENCINAS</t>
+          <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.05015</t>
+          <t>-12.04432</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.96337</t>
+          <t>-76.97061</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>324</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>338836</t>
+          <t>605434</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1211 JOSE MARIA ARGUEDAS ALTAMIRANO</t>
+          <t>153 FORTALEZA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.04679</t>
+          <t>-12.02847</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.95845</t>
+          <t>-76.94514</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>321</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>338841</t>
+          <t>780932</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1219 JOSE CARLOS MARIATEGUI</t>
+          <t>MAHANAIM</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.04534</t>
+          <t>-12.03702</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.95422</t>
+          <t>-76.96868</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>363</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>338855</t>
+          <t>338676</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1221 MARIA PARADO DE BELLIDO</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.0397</t>
+          <t>-12.04078</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.96022</t>
+          <t>-76.9866</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>345</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>338879</t>
+          <t>339690</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1253 FRANCISCO BOLOGNESI</t>
+          <t>SAN AGUSTIN</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.03969</t>
+          <t>-12.03146</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.96191</t>
+          <t>-76.96053</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>610</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>338884</t>
+          <t>339826</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1256 ALFONSO UGARTE</t>
+          <t>VIRGEN DE FATIMA MILAGROSA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.03028</t>
+          <t>-12.03809</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.95218</t>
+          <t>-76.96272</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>253</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>338898</t>
+          <t>540904</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1273 MI PERU</t>
+          <t>CESAR VALLEJO DE LAS PRADERAS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.0312</t>
+          <t>-12.0329</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.94655</t>
+          <t>-76.96281</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>352</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,27 +1803,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>338902</t>
+          <t>338879</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JUAN VALER SANDOVAL</t>
+          <t>1253 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.03117</t>
+          <t>-12.03969</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.9591</t>
+          <t>-76.96191</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>487</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>338916</t>
+          <t>338902</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>RODOLFO HORACIO ZEBALLOS GAMES</t>
+          <t>JUAN VALER SANDOVAL</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.03202</t>
+          <t>-12.03117</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.96276</t>
+          <t>-76.9591</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>455</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>339261</t>
+          <t>338898</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ALFONSO UGARTE</t>
+          <t>1273 MI PERU</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.04823</t>
+          <t>-12.0312</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.97547</t>
+          <t>-76.94655</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>574</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,37 +1989,37 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>339317</t>
+          <t>339614</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO</t>
+          <t>MONITOR HUASCAR</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.0438</t>
+          <t>-12.04313</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.97591</t>
+          <t>-76.97796</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>625</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2051,37 +2051,37 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>339416</t>
+          <t>339893</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FRAY PEDRO URRACA</t>
+          <t>WILLIAM SHAKESPEARE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.04273</t>
+          <t>-12.02888</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.9854</t>
+          <t>-76.94631</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2113,27 +2113,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>339614</t>
+          <t>552893</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MONITOR HUASCAR</t>
+          <t>DORADO SCHOOL</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.04313</t>
+          <t>-12.03148</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.97796</t>
+          <t>-76.94955</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>232</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>339652</t>
+          <t>629388</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>CIBERT SANTA ANITA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.04432</t>
+          <t>-12.04325</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.97061</t>
+          <t>-76.97251</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>205</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>339690</t>
+          <t>339973</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN</t>
+          <t>RICARDO PALMA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.03146</t>
+          <t>-12.04073</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.96053</t>
+          <t>-76.96935</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>506</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>339826</t>
+          <t>338756</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>VIRGEN DE FATIMA MILAGROSA</t>
+          <t>0124 GLORIOSA LEGION CACERES</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.03809</t>
+          <t>-12.05231</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.96272</t>
+          <t>-76.98433</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>686</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>339831</t>
+          <t>338916</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>INGENIEROS &amp; ARQUITECTOS UNI</t>
+          <t>RODOLFO HORACIO ZEBALLOS GAMES</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.04967</t>
+          <t>-12.03202</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.97754</t>
+          <t>-76.96276</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>667</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>339893</t>
+          <t>338742</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>WILLIAM SHAKESPEARE</t>
+          <t>123 LOS ARBOLES</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.02888</t>
+          <t>-12.045935</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.94631</t>
+          <t>-76.984783</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>742</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>339973</t>
+          <t>338681</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RICARDO PALMA</t>
+          <t>0097 PATRICIA ANTONIA LOPEZ</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.04073</t>
+          <t>-12.050626</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.96935</t>
+          <t>-76.980906</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>716</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>402605</t>
+          <t>338841</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TRILCE DE SANTA ANITA</t>
+          <t>1219 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.03276</t>
+          <t>-12.04534</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.95225</t>
+          <t>-76.95422</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>837</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>540904</t>
+          <t>338723</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO DE LAS PRADERAS</t>
+          <t>0108 SANTA ROSA DE QUIVES</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.0329</t>
+          <t>-12.05326</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.96281</t>
+          <t>-76.97946</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>925</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>549235</t>
+          <t>402605</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TECHNOLOGY SCHOOLS DE SANTA ANITA</t>
+          <t>TRILCE DE SANTA ANITA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.04639</t>
+          <t>-12.03276</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.95759</t>
+          <t>-76.95225</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>614</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>552893</t>
+          <t>722169</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>DORADO SCHOOL</t>
+          <t>TECHNOLOGY SCHOOLS DE LOS FICUS I</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.03148</t>
+          <t>-12.0465</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.94955</t>
+          <t>-76.97565</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>850</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>605434</t>
+          <t>549235</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>153 FORTALEZA</t>
+          <t>TECHNOLOGY SCHOOLS DE SANTA ANITA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.02847</t>
+          <t>-12.04639</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.94514</t>
+          <t>-76.95759</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>769</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>619450</t>
+          <t>846315</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TECHNOLOGY SCHOOLS LUCUMOS</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.0302</t>
+          <t>-12.04873</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.95442</t>
+          <t>-76.97141</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>782</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>629388</t>
+          <t>338884</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CIBERT SANTA ANITA</t>
+          <t>1256 ALFONSO UGARTE</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.04325</t>
+          <t>-12.03028</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-76.97251</t>
+          <t>-76.95218</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,37 +3043,37 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>720684</t>
+          <t>845702</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>BOURBAKI</t>
+          <t>SACO OLIVEROS HELICOIDAL</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.04457</t>
+          <t>-12.0418</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-76.97474</t>
+          <t>-76.95632</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>721122</t>
+          <t>338836</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>LA VILLA DE SANTO MARTIN</t>
+          <t>1211 JOSE MARIA ARGUEDAS ALTAMIRANO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.04245</t>
+          <t>-12.04679</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.96174</t>
+          <t>-76.95845</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>810</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>721179</t>
+          <t>860896</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LOS EDUCADORES</t>
+          <t>RED SCHOOL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.03531</t>
+          <t>-12.05405</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-76.96534</t>
+          <t>-76.97715</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>722169</t>
+          <t>338761</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TECHNOLOGY SCHOOLS DE LOS FICUS I</t>
+          <t>129 YAMAGUCHI</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.0465</t>
+          <t>-12.0485</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-76.97565</t>
+          <t>-76.97721</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>777289</t>
+          <t>339261</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MIS PRIMEROS PASOS</t>
+          <t>ALFONSO UGARTE</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.03554</t>
+          <t>-12.04823</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-76.96428</t>
+          <t>-76.97547</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>780932</t>
+          <t>338855</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MAHANAIM</t>
+          <t>1221 MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.03702</t>
+          <t>-12.0397</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-76.96868</t>
+          <t>-76.96022</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>845702</t>
+          <t>338704</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS HELICOIDAL</t>
+          <t>0106 ABRAHAM VALDELOMAR / 106 ABRAHAM VALDELOMAR</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.0418</t>
+          <t>-12.04765</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-76.95632</t>
+          <t>-76.97062</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>846315</t>
+          <t>721179</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SAN MARTIN DE PORRES</t>
+          <t>LOS EDUCADORES</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.04873</t>
+          <t>-12.03531</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-76.97141</t>
+          <t>-76.96534</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>261</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,37 +3539,37 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>860896</t>
+          <t>338695</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RED SCHOOL</t>
+          <t>0101 SHUJI KITAMURA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.05405</t>
+          <t>-12.04268</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-76.97715</t>
+          <t>-76.97738</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-SANTA_ANITA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-SANTA_ANITA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>338643</t>
+          <t>860896</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>056 VIRGEN DE FATIMA</t>
+          <t>RED SCHOOL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.04921</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.96923</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>-12.05405</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.97715</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>777289</t>
+          <t>846315</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MIS PRIMEROS PASOS</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.03554</t>
+          <t>782</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.96428</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>-12.04873</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.97141</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>338817</t>
+          <t>845702</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1137 JOSE ANTONIO ENCINAS</t>
+          <t>SACO OLIVEROS HELICOIDAL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.05015</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.96337</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>-12.0418</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-76.95632</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>338737</t>
+          <t>780932</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>MAHANAIM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.04826</t>
+          <t>363</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.96862</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>-12.03702</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.96868</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>338780</t>
+          <t>777289</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>MIS PRIMEROS PASOS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.03922</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.95862</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>-12.03554</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.96428</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>721122</t>
+          <t>722169</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LA VILLA DE SANTO MARTIN</t>
+          <t>TECHNOLOGY SCHOOLS DE LOS FICUS I</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.04245</t>
+          <t>850</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.96174</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-12.0465</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.97565</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>339416</t>
+          <t>721179</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FRAY PEDRO URRACA</t>
+          <t>LOS EDUCADORES</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.04273</t>
+          <t>261</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.9854</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-12.03531</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.96534</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>720684</t>
+          <t>721122</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BOURBAKI</t>
+          <t>LA VILLA DE SANTO MARTIN</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.04457</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.97474</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-12.04245</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.96174</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,37 +997,37 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>619450</t>
+          <t>720684</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TECHNOLOGY SCHOOLS LUCUMOS</t>
+          <t>BOURBAKI</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.0302</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.95442</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>-12.04457</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.97474</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>339317</t>
+          <t>629388</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO</t>
+          <t>CIBERT SANTA ANITA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.0438</t>
+          <t>205</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.97591</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>-12.04325</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.97251</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>338624</t>
+          <t>619450</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>053 SANTA ROSITA</t>
+          <t>TECHNOLOGY SCHOOLS LUCUMOS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.04821</t>
+          <t>760</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.97774</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>-12.0302</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.95442</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>338657</t>
+          <t>605434</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>064</t>
+          <t>153 FORTALEZA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.041</t>
+          <t>321</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.9682</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>-12.02847</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.94514</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>338799</t>
+          <t>552893</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>DORADO SCHOOL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.03233</t>
+          <t>232</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.95113</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>-12.03148</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.94955</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>339831</t>
+          <t>549235</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>INGENIEROS &amp; ARQUITECTOS UNI</t>
+          <t>TECHNOLOGY SCHOOLS DE SANTA ANITA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.04967</t>
+          <t>769</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.97754</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>-12.04639</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.95759</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>339652</t>
+          <t>540904</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>CESAR VALLEJO DE LAS PRADERAS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.04432</t>
+          <t>352</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.97061</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>-12.0329</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.96281</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>605434</t>
+          <t>402605</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>153 FORTALEZA</t>
+          <t>TRILCE DE SANTA ANITA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.02847</t>
+          <t>614</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.94514</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>-12.03276</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.95225</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>780932</t>
+          <t>339973</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MAHANAIM</t>
+          <t>RICARDO PALMA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.03702</t>
+          <t>506</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.96868</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>-12.04073</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.96935</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>338676</t>
+          <t>339911</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>JUAN ESPINOZA MEDRANO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.04078</t>
+          <t>738</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.9866</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>-12.03199</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.95977</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>339690</t>
+          <t>339893</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SAN AGUSTIN</t>
+          <t>WILLIAM SHAKESPEARE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.03146</t>
+          <t>330</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.96053</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>-12.02888</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.94631</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>339826</t>
+          <t>339831</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VIRGEN DE FATIMA MILAGROSA</t>
+          <t>INGENIEROS &amp; ARQUITECTOS UNI</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.03809</t>
+          <t>257</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.96272</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>-12.04967</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.97754</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>540904</t>
+          <t>339826</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO DE LAS PRADERAS</t>
+          <t>VIRGEN DE FATIMA MILAGROSA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.0329</t>
+          <t>253</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.96281</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>-12.03809</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.96272</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>338879</t>
+          <t>339690</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1253 FRANCISCO BOLOGNESI</t>
+          <t>SAN AGUSTIN</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.03969</t>
+          <t>610</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.96191</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>-12.03146</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.96053</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>338902</t>
+          <t>339652</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JUAN VALER SANDOVAL</t>
+          <t>NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.03117</t>
+          <t>324</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.9591</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>-12.04432</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.97061</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,37 +1927,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>338898</t>
+          <t>339614</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1273 MI PERU</t>
+          <t>MONITOR HUASCAR</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.0312</t>
+          <t>625</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.94655</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>-12.04313</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-76.97796</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>339614</t>
+          <t>339416</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MONITOR HUASCAR</t>
+          <t>FRAY PEDRO URRACA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.04313</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.97796</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>-12.04273</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.9854</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>339893</t>
+          <t>339317</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>WILLIAM SHAKESPEARE</t>
+          <t>CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.02888</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.94631</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>-12.0438</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.97591</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>552893</t>
+          <t>339261</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>DORADO SCHOOL</t>
+          <t>ALFONSO UGARTE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.03148</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.94955</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>-12.04823</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.97547</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>629388</t>
+          <t>338916</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CIBERT SANTA ANITA</t>
+          <t>RODOLFO HORACIO ZEBALLOS GAMES</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.04325</t>
+          <t>667</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.97251</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>-12.03202</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-76.96276</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>339973</t>
+          <t>338902</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RICARDO PALMA</t>
+          <t>JUAN VALER SANDOVAL</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.04073</t>
+          <t>455</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.96935</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>-12.03117</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-76.9591</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>338756</t>
+          <t>338898</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0124 GLORIOSA LEGION CACERES</t>
+          <t>1273 MI PERU</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.05231</t>
+          <t>574</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.98433</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>-12.0312</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-76.94655</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>338916</t>
+          <t>338884</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RODOLFO HORACIO ZEBALLOS GAMES</t>
+          <t>1256 ALFONSO UGARTE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.03202</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.96276</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>-12.03028</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-76.95218</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>338742</t>
+          <t>338879</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>123 LOS ARBOLES</t>
+          <t>1253 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.045935</t>
+          <t>487</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.984783</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>-12.03969</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-76.96191</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>339911</t>
+          <t>338855</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>JUAN ESPINOZA MEDRANO</t>
+          <t>1221 MARIA PARADO DE BELLIDO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.03199</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.95977</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>-12.0397</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-76.96022</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>338681</t>
+          <t>338841</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0097 PATRICIA ANTONIA LOPEZ</t>
+          <t>1219 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.050626</t>
+          <t>837</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.980906</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>-12.04534</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-76.95422</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>338841</t>
+          <t>338836</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1219 JOSE CARLOS MARIATEGUI</t>
+          <t>1211 JOSE MARIA ARGUEDAS ALTAMIRANO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.04534</t>
+          <t>810</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.95422</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>-12.04679</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-76.95845</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>338723</t>
+          <t>338817</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0108 SANTA ROSA DE QUIVES</t>
+          <t>1137 JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.05326</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.97946</t>
+          <t>104</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>-12.05015</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-76.96337</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>402605</t>
+          <t>338799</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TRILCE DE SANTA ANITA</t>
+          <t>186</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.03276</t>
+          <t>322</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.95225</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>-12.03233</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-76.95113</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>722169</t>
+          <t>338780</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TECHNOLOGY SCHOOLS DE LOS FICUS I</t>
+          <t>152</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.0465</t>
+          <t>266</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.97565</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>-12.03922</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-76.95862</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>549235</t>
+          <t>338761</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TECHNOLOGY SCHOOLS DE SANTA ANITA</t>
+          <t>129 YAMAGUCHI</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.04639</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.95759</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>-12.0485</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-76.97721</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>846315</t>
+          <t>338756</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SAN MARTIN DE PORRES</t>
+          <t>0124 GLORIOSA LEGION CACERES</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.04873</t>
+          <t>686</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.97141</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>-12.05231</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-76.98433</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>338884</t>
+          <t>338742</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1256 ALFONSO UGARTE</t>
+          <t>123 LOS ARBOLES</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.03028</t>
+          <t>742</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-76.95218</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>-12.045935</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-76.984783</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>845702</t>
+          <t>338737</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS HELICOIDAL</t>
+          <t>111</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.0418</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-76.95632</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>-12.04826</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-76.96862</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>338836</t>
+          <t>338723</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1211 JOSE MARIA ARGUEDAS ALTAMIRANO</t>
+          <t>0108 SANTA ROSA DE QUIVES</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.04679</t>
+          <t>925</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.95845</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>-12.05326</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-76.97946</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>860896</t>
+          <t>338704</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>RED SCHOOL</t>
+          <t>0106 ABRAHAM VALDELOMAR / 106 ABRAHAM VALDELOMAR</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.05405</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-76.97715</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>-12.04765</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-76.97062</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,37 +3229,37 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>338761</t>
+          <t>338695</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>129 YAMAGUCHI</t>
+          <t>0101 SHUJI KITAMURA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.0485</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-76.97721</t>
+          <t>92</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>-12.04268</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-76.97738</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>339261</t>
+          <t>338681</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ALFONSO UGARTE</t>
+          <t>0097 PATRICIA ANTONIA LOPEZ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.04823</t>
+          <t>716</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-76.97547</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>-12.050626</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-76.980906</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>338855</t>
+          <t>338676</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1221 MARIA PARADO DE BELLIDO</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.0397</t>
+          <t>345</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-76.96022</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>-12.04078</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-76.9866</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>338704</t>
+          <t>338657</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0106 ABRAHAM VALDELOMAR / 106 ABRAHAM VALDELOMAR</t>
+          <t>064</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.04765</t>
+          <t>359</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-76.97062</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>-12.041</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>-76.9682</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>721179</t>
+          <t>338643</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LOS EDUCADORES</t>
+          <t>056 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.03531</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-76.96534</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>-12.04921</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-76.96923</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,37 +3539,37 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>338695</t>
+          <t>338624</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0101 SHUJI KITAMURA</t>
+          <t>053 SANTA ROSITA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.04268</t>
+          <t>379</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-76.97738</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2447</t>
+          <t>-12.04821</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>-76.97774</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-SANTA_ANITA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-SANTA_ANITA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
